--- a/school_lublino/floors/vor_lublino_floors.xlsx
+++ b/school_lublino/floors/vor_lublino_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="14" activeTab="20"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="11" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Из1эт" sheetId="8" r:id="rId9"/>
     <sheet name="Из2эт" sheetId="9" r:id="rId10"/>
     <sheet name="ВорПленка" sheetId="12" r:id="rId11"/>
-    <sheet name="Плк1э" sheetId="13" state="hidden" r:id="rId12"/>
+    <sheet name="Плк1э" sheetId="13" r:id="rId12"/>
     <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId13"/>
     <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId14"/>
     <sheet name="Общ" sheetId="7" r:id="rId15"/>
@@ -33,6 +33,7 @@
     <sheet name="3эт" sheetId="20" r:id="rId19"/>
     <sheet name="КП" sheetId="23" r:id="rId20"/>
     <sheet name="2.1-Пл" sheetId="22" r:id="rId21"/>
+    <sheet name="3.1-Пл" sheetId="24" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="343">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1100,6 +1101,12 @@
   </si>
   <si>
     <t>3 эт. отм. +8.400</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Тип 9</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1887,6 +1894,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1917,10 +1928,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3515,13 +3553,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="167" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="167"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="169"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
@@ -3903,13 +3941,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4422,13 +4460,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="170" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4820,13 +4858,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="167"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="169"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -4963,13 +5001,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="167"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="169"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -7663,13 +7701,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -7733,13 +7771,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="168" t="s">
+      <c r="A7" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="172"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -7802,13 +7840,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="168" t="s">
+      <c r="A13" s="170" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="169"/>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
-      <c r="E13" s="170"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="171"/>
+      <c r="D13" s="171"/>
+      <c r="E13" s="172"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="85" t="s">
@@ -8303,13 +8341,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="173" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -8375,13 +8413,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="173" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="171"/>
-      <c r="C7" s="171"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="171"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -8464,13 +8502,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="173" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="85">
@@ -8518,13 +8556,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -8574,13 +8612,13 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="171" t="s">
+      <c r="A6" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="171"/>
-      <c r="D6" s="171"/>
-      <c r="E6" s="171"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="85" t="s">
@@ -9093,7 +9131,7 @@
       <c r="I2" s="126">
         <v>4905.38</v>
       </c>
-      <c r="J2" s="174">
+      <c r="J2" s="165">
         <f>'2.1-Пл'!F17</f>
         <v>1838.74</v>
       </c>
@@ -12131,18 +12169,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="176" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175" t="s">
+      <c r="B1" s="176"/>
+      <c r="C1" s="176" t="s">
         <v>339</v>
       </c>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175" t="s">
+      <c r="D1" s="176"/>
+      <c r="E1" s="176" t="s">
         <v>340</v>
       </c>
-      <c r="F1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12369,22 +12407,22 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="173" t="s">
+      <c r="A15" s="175" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="173"/>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="175"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="172" t="s">
+      <c r="A16" s="174" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="172"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="172"/>
+      <c r="B16" s="174"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
       <c r="E16" s="157" t="s">
         <v>2</v>
       </c>
@@ -12393,12 +12431,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="172" t="s">
+      <c r="A17" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="172"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="172"/>
+      <c r="B17" s="174"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="174"/>
       <c r="E17" s="157" t="s">
         <v>7</v>
       </c>
@@ -12415,6 +12453,201 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="156" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="176" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A2" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="161" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="162">
+        <v>113.98</v>
+      </c>
+      <c r="C3" s="183"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="184"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="161" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="162">
+        <v>68.63</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="184"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="161" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" s="162">
+        <v>69.02</v>
+      </c>
+      <c r="C5" s="183"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="183"/>
+      <c r="F5" s="184"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="161" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="162">
+        <v>68.94</v>
+      </c>
+      <c r="C6" s="183"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="184"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="162">
+        <v>68.849999999999994</v>
+      </c>
+      <c r="C7" s="183"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="184"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="161" t="s">
+        <v>325</v>
+      </c>
+      <c r="B8" s="162">
+        <v>67.86</v>
+      </c>
+      <c r="C8" s="183"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="183"/>
+      <c r="F8" s="184"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="161" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="162">
+        <v>139.03</v>
+      </c>
+      <c r="C9" s="183"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="184"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="162">
+        <f>SUM(B3:B9)</f>
+        <v>596.30999999999995</v>
+      </c>
+      <c r="C10" s="185"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="185"/>
+      <c r="F10" s="184"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C11" s="186"/>
+      <c r="D11" s="186"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="184"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="175" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="175"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="178" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="179"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="177" t="s">
+        <v>341</v>
+      </c>
+      <c r="E14" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="89.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="178" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="179"/>
+      <c r="C15" s="180"/>
+      <c r="D15" s="177" t="s">
+        <v>342</v>
+      </c>
+      <c r="E15" s="164" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="159">
+        <f>B10</f>
+        <v>596.30999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12433,15 +12666,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="166" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -13650,15 +13883,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="166" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -15750,13 +15983,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="167" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="167"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="169"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">

--- a/school_lublino/floors/vor_lublino_floors.xlsx
+++ b/school_lublino/floors/vor_lublino_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="11" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="20" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
@@ -34,11 +34,17 @@
     <sheet name="КП" sheetId="23" r:id="rId20"/>
     <sheet name="2.1-Пл" sheetId="22" r:id="rId21"/>
     <sheet name="3.1-Пл" sheetId="24" r:id="rId22"/>
+    <sheet name="3.2-Плен" sheetId="28" r:id="rId23"/>
+    <sheet name="4.1-Изол" sheetId="25" r:id="rId24"/>
+    <sheet name="5.1-СКБ" sheetId="26" r:id="rId25"/>
+    <sheet name="6.1-Нал.пл" sheetId="29" r:id="rId26"/>
+    <sheet name="5.2-СКБ7.1" sheetId="30" r:id="rId27"/>
+    <sheet name="7.1-Шл4.4" sheetId="31" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="360">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1107,6 +1113,58 @@
   </si>
   <si>
     <t>Тип 9</t>
+  </si>
+  <si>
+    <t>Тип 11</t>
+  </si>
+  <si>
+    <t>2.111</t>
+  </si>
+  <si>
+    <t>2.114</t>
+  </si>
+  <si>
+    <t>2.115</t>
+  </si>
+  <si>
+    <t>2.117</t>
+  </si>
+  <si>
+    <t>2.112</t>
+  </si>
+  <si>
+    <t>2.116</t>
+  </si>
+  <si>
+    <t>2.166</t>
+  </si>
+  <si>
+    <t>2.167</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 61мм до 80 мм</t>
+  </si>
+  <si>
+    <t>Тип 6.1</t>
+  </si>
+  <si>
+    <t>Тип 6.1, М200, толщиной 65 мм.</t>
+  </si>
+  <si>
+    <t>Тип 11, М200, толщиной 68 мм.</t>
+  </si>
+  <si>
+    <t>Устройство наливных полов с огрунтовкой поверхности и проклейкой демпферной лентой / толщ. до 10 мм</t>
+  </si>
+  <si>
+    <t>Устройство звукоизоляции полов / в 1 слой</t>
+  </si>
+  <si>
+    <t>Тип 11
+нахлест на стены 100 мм.</t>
+  </si>
+  <si>
+    <t>№</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1356,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1439,11 +1497,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1898,6 +1983,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1931,9 +2047,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1946,19 +2059,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3553,13 +3686,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="178" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="169"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="180"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
@@ -3941,13 +4074,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="172"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4460,13 +4593,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="181" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="172"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4858,13 +4991,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="178" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="169"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="180"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -5001,13 +5134,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="169"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="180"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -7701,13 +7834,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="172"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -7771,13 +7904,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="170" t="s">
+      <c r="A7" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="171"/>
-      <c r="C7" s="171"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="172"/>
+      <c r="B7" s="182"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="183"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -7840,13 +7973,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="170" t="s">
+      <c r="A13" s="181" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="171"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="172"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="183"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="85" t="s">
@@ -8341,13 +8474,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="184" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -8413,13 +8546,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="173" t="s">
+      <c r="A7" s="184" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="173"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
+      <c r="B7" s="184"/>
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -8502,13 +8635,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="173" t="s">
+      <c r="A14" s="184" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="173"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
+      <c r="B14" s="184"/>
+      <c r="C14" s="184"/>
+      <c r="D14" s="184"/>
+      <c r="E14" s="184"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="85">
@@ -8556,13 +8689,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="184" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -8612,13 +8745,13 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="184" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="173"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
+      <c r="B6" s="184"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="85" t="s">
@@ -12169,18 +12302,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="187" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176" t="s">
+      <c r="B1" s="187"/>
+      <c r="C1" s="187" t="s">
         <v>339</v>
       </c>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176" t="s">
+      <c r="D1" s="187"/>
+      <c r="E1" s="187" t="s">
         <v>340</v>
       </c>
-      <c r="F1" s="176"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12407,22 +12540,22 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="175" t="s">
+      <c r="A15" s="186" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="175"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="186"/>
+      <c r="F15" s="186"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="174" t="s">
+      <c r="A16" s="185" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
       <c r="E16" s="157" t="s">
         <v>2</v>
       </c>
@@ -12431,12 +12564,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="174" t="s">
+      <c r="A17" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="174"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
       <c r="E17" s="157" t="s">
         <v>7</v>
       </c>
@@ -12473,14 +12606,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="187" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12489,10 +12622,10 @@
       <c r="B2" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="161" t="s">
@@ -12501,10 +12634,10 @@
       <c r="B3" s="162">
         <v>113.98</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="184"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="170"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="161" t="s">
@@ -12513,10 +12646,10 @@
       <c r="B4" s="162">
         <v>68.63</v>
       </c>
-      <c r="C4" s="183"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="184"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="170"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="170"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -12525,10 +12658,10 @@
       <c r="B5" s="162">
         <v>69.02</v>
       </c>
-      <c r="C5" s="183"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="184"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="170"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -12537,10 +12670,10 @@
       <c r="B6" s="162">
         <v>68.94</v>
       </c>
-      <c r="C6" s="183"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="184"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="170"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -12549,10 +12682,10 @@
       <c r="B7" s="162">
         <v>68.849999999999994</v>
       </c>
-      <c r="C7" s="183"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="184"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="170"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -12561,10 +12694,10 @@
       <c r="B8" s="162">
         <v>67.86</v>
       </c>
-      <c r="C8" s="183"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="184"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="169"/>
+      <c r="F8" s="170"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="161" t="s">
@@ -12573,10 +12706,10 @@
       <c r="B9" s="162">
         <v>139.03</v>
       </c>
-      <c r="C9" s="183"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="184"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="170"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="163" t="s">
@@ -12586,34 +12719,34 @@
         <f>SUM(B3:B9)</f>
         <v>596.30999999999995</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="184"/>
+      <c r="C10" s="171"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="171"/>
+      <c r="F10" s="170"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="186"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="184"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="170"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="175" t="s">
+      <c r="A13" s="186" t="s">
         <v>317</v>
       </c>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
+      <c r="B13" s="186"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="186"/>
+      <c r="F13" s="186"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="178" t="s">
+      <c r="A14" s="188" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="177" t="s">
+      <c r="B14" s="189"/>
+      <c r="C14" s="190"/>
+      <c r="D14" s="167" t="s">
         <v>341</v>
       </c>
       <c r="E14" s="164" t="s">
@@ -12624,12 +12757,12 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="89.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="178" t="s">
+      <c r="A15" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="179"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="177" t="s">
+      <c r="B15" s="189"/>
+      <c r="C15" s="190"/>
+      <c r="D15" s="167" t="s">
         <v>342</v>
       </c>
       <c r="E15" s="164" t="s">
@@ -12642,12 +12775,783 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="23" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="156" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="188" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="189"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="192" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="193"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="167" t="s">
+        <v>343</v>
+      </c>
+      <c r="E3" s="173" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="159">
+        <f>B9</f>
+        <v>115.60000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="195"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="161" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="162">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="161" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" s="162">
+        <v>56.31</v>
+      </c>
+      <c r="C6" s="197"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="198"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="162">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="C7" s="197"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="161" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8" s="162">
+        <v>11.97</v>
+      </c>
+      <c r="C8" s="197"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="162">
+        <f>SUM(B5:B8)</f>
+        <v>115.60000000000001</v>
+      </c>
+      <c r="C9" s="197"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="198"/>
+      <c r="F9" s="198"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="C4:F9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="156" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="156" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="188" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="189"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="192" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="193"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="167" t="s">
+        <v>358</v>
+      </c>
+      <c r="E3" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="159">
+        <f>B9</f>
+        <v>1923.9773</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="195"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="161" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="162">
+        <f>379.31+(84.163-4)*0.1</f>
+        <v>387.3263</v>
+      </c>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="161" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="162">
+        <f>381.65+(83.53-2.2-1.8)*0.1</f>
+        <v>389.60299999999995</v>
+      </c>
+      <c r="C6" s="197"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="198"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="162">
+        <f>563.46+(102.28-1.5-2.2)*0.1</f>
+        <v>573.31799999999998</v>
+      </c>
+      <c r="C7" s="197"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="161" t="s">
+        <v>347</v>
+      </c>
+      <c r="B8" s="162">
+        <f>563.73+10</f>
+        <v>573.73</v>
+      </c>
+      <c r="C8" s="197"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="162">
+        <f>SUM(B5:B8)</f>
+        <v>1923.9773</v>
+      </c>
+      <c r="C9" s="197"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="198"/>
+      <c r="F9" s="198"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="C4:F9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" style="156" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="156" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="188" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="189"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="192" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="193"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="167" t="s">
+        <v>354</v>
+      </c>
+      <c r="E3" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="159">
+        <f>F11</f>
+        <v>115.60000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="192" t="s">
+        <v>352</v>
+      </c>
+      <c r="B4" s="193"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="167" t="s">
+        <v>355</v>
+      </c>
+      <c r="E4" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="159">
+        <f>B11</f>
+        <v>1888.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="188" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="188" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="190"/>
+    </row>
+    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A6" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="201"/>
+      <c r="D6" s="202"/>
+      <c r="E6" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="F6" s="160" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="162">
+        <v>379.31</v>
+      </c>
+      <c r="C7" s="201"/>
+      <c r="D7" s="202"/>
+      <c r="E7" s="161" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="162">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="161" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="162">
+        <v>381.65</v>
+      </c>
+      <c r="C8" s="201"/>
+      <c r="D8" s="202"/>
+      <c r="E8" s="161" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" s="162">
+        <v>56.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="161" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="162">
+        <v>563.46</v>
+      </c>
+      <c r="C9" s="201"/>
+      <c r="D9" s="202"/>
+      <c r="E9" s="161" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9" s="162">
+        <v>10.119999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="161" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="162">
+        <v>563.73</v>
+      </c>
+      <c r="C10" s="201"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="161" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" s="162">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="162">
+        <f>SUM(B7:B10)</f>
+        <v>1888.15</v>
+      </c>
+      <c r="C11" s="201"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="F11" s="162">
+        <f>SUM(F7:F10)</f>
+        <v>115.60000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="C5:D11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="156" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="188" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="189"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="67.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="192" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" s="193"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="167" t="s">
+        <v>343</v>
+      </c>
+      <c r="E3" s="173" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="159">
+        <f>B9</f>
+        <v>1888.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="195"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="161" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="162">
+        <v>379.31</v>
+      </c>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="161" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="162">
+        <v>381.65</v>
+      </c>
+      <c r="C6" s="197"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="198"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="161" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="162">
+        <v>563.46</v>
+      </c>
+      <c r="C7" s="197"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="161" t="s">
+        <v>347</v>
+      </c>
+      <c r="B8" s="162">
+        <v>563.73</v>
+      </c>
+      <c r="C8" s="197"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="162">
+        <f>SUM(B5:B8)</f>
+        <v>1888.15</v>
+      </c>
+      <c r="C9" s="197"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="198"/>
+      <c r="F9" s="198"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="C4:F9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="156"/>
+    <col min="2" max="2" width="49.6640625" style="156" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="156" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="174" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="174" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="174" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="174">
+        <v>1</v>
+      </c>
+      <c r="B3" s="176" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="167" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="174" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="159">
+        <v>46.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="156"/>
+    <col min="2" max="2" width="49.6640625" style="156" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="156" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="186" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="175" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="175" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="175">
+        <v>1</v>
+      </c>
+      <c r="B3" s="176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="175" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="159">
+        <v>72.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12666,15 +13570,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="177" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -13883,15 +14787,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="177" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -15983,13 +16887,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="178" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="169"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="180"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">

--- a/school_lublino/floors/vor_lublino_floors.xlsx
+++ b/school_lublino/floors/vor_lublino_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="20" activeTab="27"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="20" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
@@ -39,7 +39,8 @@
     <sheet name="5.1-СКБ" sheetId="26" r:id="rId25"/>
     <sheet name="6.1-Нал.пл" sheetId="29" r:id="rId26"/>
     <sheet name="5.2-СКБ7.1" sheetId="30" r:id="rId27"/>
-    <sheet name="7.1-Шл4.4" sheetId="31" r:id="rId28"/>
+    <sheet name="7.1-Шл4.4" sheetId="32" r:id="rId28"/>
+    <sheet name="7.2-Гидр5" sheetId="31" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="366">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1165,6 +1166,24 @@
   </si>
   <si>
     <t>№</t>
+  </si>
+  <si>
+    <t>Тип 5, 5.1</t>
+  </si>
+  <si>
+    <t>№ Блок</t>
+  </si>
+  <si>
+    <t>1 этаж</t>
+  </si>
+  <si>
+    <t>2 этаж</t>
+  </si>
+  <si>
+    <t>3 этаж</t>
+  </si>
+  <si>
+    <t>Итог:</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2014,6 +2033,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2091,6 +2113,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3686,13 +3717,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="179" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="180"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="181"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
@@ -4074,13 +4105,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="182" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4593,13 +4624,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="182" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4991,13 +5022,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="179" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="180"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="181"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -5134,13 +5165,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="179" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="180"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="181"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -7834,13 +7865,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="182" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -7904,13 +7935,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="182" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="183"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="184"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -7973,13 +8004,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="182"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="183"/>
+      <c r="B13" s="183"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="184"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="85" t="s">
@@ -8474,13 +8505,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -8546,13 +8577,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="185" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
+      <c r="B7" s="185"/>
+      <c r="C7" s="185"/>
+      <c r="D7" s="185"/>
+      <c r="E7" s="185"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -8635,13 +8666,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="185" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="85">
@@ -8689,13 +8720,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -8745,13 +8776,13 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="185" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
+      <c r="B6" s="185"/>
+      <c r="C6" s="185"/>
+      <c r="D6" s="185"/>
+      <c r="E6" s="185"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="85" t="s">
@@ -12302,18 +12333,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="188" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187" t="s">
+      <c r="B1" s="188"/>
+      <c r="C1" s="188" t="s">
         <v>339</v>
       </c>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187" t="s">
+      <c r="D1" s="188"/>
+      <c r="E1" s="188" t="s">
         <v>340</v>
       </c>
-      <c r="F1" s="187"/>
+      <c r="F1" s="188"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12540,22 +12571,22 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="186" t="s">
+      <c r="A15" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
+      <c r="B15" s="187"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="185" t="s">
+      <c r="A16" s="186" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="186"/>
       <c r="E16" s="157" t="s">
         <v>2</v>
       </c>
@@ -12564,12 +12595,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="185" t="s">
+      <c r="A17" s="186" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="186"/>
       <c r="E17" s="157" t="s">
         <v>7</v>
       </c>
@@ -12606,14 +12637,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="188" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
-      <c r="E1" s="191"/>
-      <c r="F1" s="191"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12731,21 +12762,21 @@
       <c r="F11" s="170"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="186" t="s">
+      <c r="A13" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-      <c r="F13" s="186"/>
+      <c r="B13" s="187"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="187"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="188" t="s">
+      <c r="A14" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="189"/>
-      <c r="C14" s="190"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="191"/>
       <c r="D14" s="167" t="s">
         <v>341</v>
       </c>
@@ -12757,11 +12788,11 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="89.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="188" t="s">
+      <c r="A15" s="189" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="189"/>
-      <c r="C15" s="190"/>
+      <c r="B15" s="190"/>
+      <c r="C15" s="191"/>
       <c r="D15" s="167" t="s">
         <v>342</v>
       </c>
@@ -12804,21 +12835,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="190"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="191"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -12830,11 +12861,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="194"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="195"/>
       <c r="D3" s="167" t="s">
         <v>343</v>
       </c>
@@ -12853,10 +12884,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="195"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -12865,10 +12896,10 @@
       <c r="B5" s="162">
         <v>37.200000000000003</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -12877,10 +12908,10 @@
       <c r="B6" s="162">
         <v>56.31</v>
       </c>
-      <c r="C6" s="197"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="199"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -12889,10 +12920,10 @@
       <c r="B7" s="162">
         <v>10.119999999999999</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -12901,10 +12932,10 @@
       <c r="B8" s="162">
         <v>11.97</v>
       </c>
-      <c r="C8" s="197"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="198"/>
-      <c r="F8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="199"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="199"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -12914,10 +12945,10 @@
         <f>SUM(B5:B8)</f>
         <v>115.60000000000001</v>
       </c>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12948,21 +12979,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="190"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="191"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -12974,11 +13005,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="193" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="194"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="195"/>
       <c r="D3" s="167" t="s">
         <v>358</v>
       </c>
@@ -12997,10 +13028,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="195"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -13010,10 +13041,10 @@
         <f>379.31+(84.163-4)*0.1</f>
         <v>387.3263</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -13023,10 +13054,10 @@
         <f>381.65+(83.53-2.2-1.8)*0.1</f>
         <v>389.60299999999995</v>
       </c>
-      <c r="C6" s="197"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="199"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -13036,10 +13067,10 @@
         <f>563.46+(102.28-1.5-2.2)*0.1</f>
         <v>573.31799999999998</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -13049,10 +13080,10 @@
         <f>563.73+10</f>
         <v>573.73</v>
       </c>
-      <c r="C8" s="197"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="198"/>
-      <c r="F8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="199"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="199"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -13062,10 +13093,10 @@
         <f>SUM(B5:B8)</f>
         <v>1923.9773</v>
       </c>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13096,21 +13127,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="190"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="191"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13122,11 +13153,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="193" t="s">
         <v>352</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="194"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="195"/>
       <c r="D3" s="167" t="s">
         <v>354</v>
       </c>
@@ -13139,11 +13170,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="192" t="s">
+      <c r="A4" s="193" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="193"/>
-      <c r="C4" s="194"/>
+      <c r="B4" s="194"/>
+      <c r="C4" s="195"/>
       <c r="D4" s="167" t="s">
         <v>355</v>
       </c>
@@ -13156,16 +13187,16 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="188" t="s">
+      <c r="A5" s="189" t="s">
         <v>343</v>
       </c>
-      <c r="B5" s="190"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="188" t="s">
+      <c r="B5" s="191"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="189" t="s">
         <v>353</v>
       </c>
-      <c r="F5" s="190"/>
+      <c r="F5" s="191"/>
     </row>
     <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="160" t="s">
@@ -13174,8 +13205,8 @@
       <c r="B6" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="201"/>
-      <c r="D6" s="202"/>
+      <c r="C6" s="202"/>
+      <c r="D6" s="203"/>
       <c r="E6" s="160" t="s">
         <v>318</v>
       </c>
@@ -13190,8 +13221,8 @@
       <c r="B7" s="162">
         <v>379.31</v>
       </c>
-      <c r="C7" s="201"/>
-      <c r="D7" s="202"/>
+      <c r="C7" s="202"/>
+      <c r="D7" s="203"/>
       <c r="E7" s="161" t="s">
         <v>348</v>
       </c>
@@ -13206,8 +13237,8 @@
       <c r="B8" s="162">
         <v>381.65</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="202"/>
+      <c r="C8" s="202"/>
+      <c r="D8" s="203"/>
       <c r="E8" s="161" t="s">
         <v>349</v>
       </c>
@@ -13222,8 +13253,8 @@
       <c r="B9" s="162">
         <v>563.46</v>
       </c>
-      <c r="C9" s="201"/>
-      <c r="D9" s="202"/>
+      <c r="C9" s="202"/>
+      <c r="D9" s="203"/>
       <c r="E9" s="161" t="s">
         <v>350</v>
       </c>
@@ -13238,8 +13269,8 @@
       <c r="B10" s="162">
         <v>563.73</v>
       </c>
-      <c r="C10" s="201"/>
-      <c r="D10" s="202"/>
+      <c r="C10" s="202"/>
+      <c r="D10" s="203"/>
       <c r="E10" s="161" t="s">
         <v>351</v>
       </c>
@@ -13255,8 +13286,8 @@
         <f>SUM(B7:B10)</f>
         <v>1888.15</v>
       </c>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="203"/>
       <c r="E11" s="163" t="s">
         <v>337</v>
       </c>
@@ -13297,21 +13328,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="190"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="191"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13323,11 +13354,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="67.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="193" t="s">
         <v>356</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="194"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="195"/>
       <c r="D3" s="167" t="s">
         <v>343</v>
       </c>
@@ -13346,10 +13377,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="195"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -13358,10 +13389,10 @@
       <c r="B5" s="162">
         <v>379.31</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -13370,10 +13401,10 @@
       <c r="B6" s="162">
         <v>381.65</v>
       </c>
-      <c r="C6" s="197"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="199"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -13382,10 +13413,10 @@
       <c r="B7" s="162">
         <v>563.46</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -13394,10 +13425,10 @@
       <c r="B8" s="162">
         <v>563.73</v>
       </c>
-      <c r="C8" s="197"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="198"/>
-      <c r="F8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="199"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="199"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -13407,10 +13438,10 @@
         <f>SUM(B5:B8)</f>
         <v>1888.15</v>
       </c>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13440,13 +13471,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="174" t="s">
@@ -13507,25 +13538,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="177" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="177" t="s">
         <v>302</v>
       </c>
       <c r="C2" s="167" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="175" t="s">
+      <c r="D2" s="177" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="158" t="s">
@@ -13533,7 +13564,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="175">
+      <c r="A3" s="177">
         <v>1</v>
       </c>
       <c r="B3" s="176" t="s">
@@ -13542,7 +13573,7 @@
       <c r="C3" s="167" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="175" t="s">
+      <c r="D3" s="177" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="159">
@@ -13554,6 +13585,167 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="156" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="156" customWidth="1"/>
+    <col min="3" max="4" width="14.109375" style="156" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="156" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="156" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="156" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="156" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="187" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="175" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="189" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="G2" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="175">
+        <v>1</v>
+      </c>
+      <c r="B3" s="193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="167" t="s">
+        <v>360</v>
+      </c>
+      <c r="G3" s="175" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="159">
+        <f>D8</f>
+        <v>47.740000000000009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="204"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="163" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" s="163" t="s">
+        <v>362</v>
+      </c>
+      <c r="C5" s="163" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="163" t="s">
+        <v>364</v>
+      </c>
+      <c r="E5" s="205"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="206"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="163">
+        <v>1</v>
+      </c>
+      <c r="B6" s="163">
+        <v>11.69</v>
+      </c>
+      <c r="C6" s="163">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="D6" s="163">
+        <v>6.03</v>
+      </c>
+      <c r="E6" s="205"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="163">
+        <v>7.73</v>
+      </c>
+      <c r="C7" s="163">
+        <v>8.09</v>
+      </c>
+      <c r="D7" s="163">
+        <v>5.92</v>
+      </c>
+      <c r="E7" s="205"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C8" s="163" t="s">
+        <v>365</v>
+      </c>
+      <c r="D8" s="163">
+        <f>SUM(B6:D7)</f>
+        <v>47.740000000000009</v>
+      </c>
+      <c r="E8" s="205"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="E5:H8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13570,15 +13762,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -14787,15 +14979,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -16887,13 +17079,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="179" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="180"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="181"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">

--- a/school_lublino/floors/vor_lublino_floors.xlsx
+++ b/school_lublino/floors/vor_lublino_floors.xlsx
@@ -9,41 +9,42 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="20" activeTab="28"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14196" windowHeight="6840" tabRatio="836" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
     <sheet name="ВОР 2 эт" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Спец 2 эт" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="ВОР 3 эт" sheetId="3" state="hidden" r:id="rId4"/>
-    <sheet name="Спец 3 эт" sheetId="6" r:id="rId5"/>
-    <sheet name="общий (2)" sheetId="5" state="hidden" r:id="rId6"/>
-    <sheet name="не сделали" sheetId="21" r:id="rId7"/>
-    <sheet name="ВорИзол" sheetId="10" r:id="rId8"/>
-    <sheet name="Из1эт" sheetId="8" r:id="rId9"/>
-    <sheet name="Из2эт" sheetId="9" r:id="rId10"/>
-    <sheet name="ВорПленка" sheetId="12" r:id="rId11"/>
-    <sheet name="Плк1э" sheetId="13" r:id="rId12"/>
-    <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId13"/>
-    <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId14"/>
-    <sheet name="Общ" sheetId="7" r:id="rId15"/>
-    <sheet name="СКБ-1эт" sheetId="17" r:id="rId16"/>
-    <sheet name="1эт" sheetId="18" r:id="rId17"/>
-    <sheet name="2эт" sheetId="19" r:id="rId18"/>
-    <sheet name="3эт" sheetId="20" r:id="rId19"/>
-    <sheet name="КП" sheetId="23" r:id="rId20"/>
-    <sheet name="2.1-Пл" sheetId="22" r:id="rId21"/>
-    <sheet name="3.1-Пл" sheetId="24" r:id="rId22"/>
-    <sheet name="3.2-Плен" sheetId="28" r:id="rId23"/>
-    <sheet name="4.1-Изол" sheetId="25" r:id="rId24"/>
-    <sheet name="5.1-СКБ" sheetId="26" r:id="rId25"/>
-    <sheet name="6.1-Нал.пл" sheetId="29" r:id="rId26"/>
-    <sheet name="5.2-СКБ7.1" sheetId="30" r:id="rId27"/>
-    <sheet name="7.1-Шл4.4" sheetId="32" r:id="rId28"/>
-    <sheet name="7.2-Гидр5" sheetId="31" r:id="rId29"/>
+    <sheet name="7.3Пл6" sheetId="33" r:id="rId5"/>
+    <sheet name="Спец 3 эт" sheetId="6" r:id="rId6"/>
+    <sheet name="общий (2)" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="не сделали" sheetId="21" r:id="rId8"/>
+    <sheet name="ВорИзол" sheetId="10" r:id="rId9"/>
+    <sheet name="Из1эт" sheetId="8" r:id="rId10"/>
+    <sheet name="Из2эт" sheetId="9" r:id="rId11"/>
+    <sheet name="ВорПленка" sheetId="12" r:id="rId12"/>
+    <sheet name="Плк1э" sheetId="13" r:id="rId13"/>
+    <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="Общ" sheetId="7" r:id="rId16"/>
+    <sheet name="СКБ-1эт" sheetId="17" r:id="rId17"/>
+    <sheet name="1эт" sheetId="18" r:id="rId18"/>
+    <sheet name="2эт" sheetId="19" r:id="rId19"/>
+    <sheet name="3эт" sheetId="20" r:id="rId20"/>
+    <sheet name="КП" sheetId="23" r:id="rId21"/>
+    <sheet name="2.1-Пл" sheetId="22" r:id="rId22"/>
+    <sheet name="3.1-Пл" sheetId="24" r:id="rId23"/>
+    <sheet name="3.2-Плен" sheetId="28" r:id="rId24"/>
+    <sheet name="4.1-Изол" sheetId="25" r:id="rId25"/>
+    <sheet name="5.1-СКБ" sheetId="26" r:id="rId26"/>
+    <sheet name="6.1-Нал.пл" sheetId="29" r:id="rId27"/>
+    <sheet name="5.2-СКБ7.1" sheetId="30" r:id="rId28"/>
+    <sheet name="7.1-Шл4.4" sheetId="32" r:id="rId29"/>
+    <sheet name="7.2-Гидр5" sheetId="31" r:id="rId30"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="373">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1184,6 +1185,27 @@
   </si>
   <si>
     <t>Итог:</t>
+  </si>
+  <si>
+    <t>Поз</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола СКБ с затиркой и укрытием ДВП / из керамогранитной плитки от 0,2м2/шт</t>
+  </si>
+  <si>
+    <t>Пом</t>
+  </si>
+  <si>
+    <t>1.053</t>
+  </si>
+  <si>
+    <t>1.054</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>1этаж, блок 4.1. Пол Тип: 6, 7, 7.1.</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2036,6 +2058,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2122,6 +2150,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3713,17 +3747,21 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.109375" style="63"/>
+    <col min="5" max="5" width="9.109375" style="61"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="179" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="181"/>
+      <c r="A1" s="181" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
@@ -3746,250 +3784,454 @@
       <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>99</v>
+      <c r="B3" s="64">
+        <v>1</v>
       </c>
       <c r="C3" s="64">
-        <v>2.0139999999999998</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>101</v>
+        <v>1.024</v>
+      </c>
+      <c r="D3" s="64">
+        <v>6</v>
       </c>
       <c r="E3" s="60">
-        <v>0</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="56">
+      <c r="A4" s="57">
         <v>2</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>99</v>
+      <c r="B4" s="64">
+        <v>4.0999999999999996</v>
       </c>
       <c r="C4" s="64">
-        <v>2.0150000000000001</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>101</v>
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D4" s="64">
+        <v>6</v>
       </c>
       <c r="E4" s="60">
-        <v>0</v>
+        <v>161.78</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="56">
+      <c r="A5" s="57">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>99</v>
+      <c r="B5" s="64">
+        <v>4.0999999999999996</v>
       </c>
       <c r="C5" s="64">
-        <v>2.016</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>101</v>
+        <v>1.046</v>
+      </c>
+      <c r="D5" s="64">
+        <v>6</v>
       </c>
       <c r="E5" s="60">
-        <v>0</v>
+        <v>161.15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="56">
+      <c r="A6" s="57">
         <v>4</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="54">
-        <v>2.089</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>101</v>
+      <c r="B6" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="64">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D6" s="64">
+        <v>6</v>
       </c>
       <c r="E6" s="60">
-        <v>0</v>
+        <v>443.48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="56">
+      <c r="A7" s="57">
         <v>5</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="54">
-        <v>2.09</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>101</v>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="64">
+        <v>1.034</v>
+      </c>
+      <c r="D7" s="64">
+        <v>7</v>
       </c>
       <c r="E7" s="60">
-        <v>0</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="56">
+      <c r="A8" s="57">
         <v>6</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="54">
-        <v>2.0910000000000002</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>101</v>
+      <c r="B8" s="64">
+        <v>1</v>
+      </c>
+      <c r="C8" s="64">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D8" s="64">
+        <v>7</v>
       </c>
       <c r="E8" s="60">
-        <v>0</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="56">
+      <c r="A9" s="57">
         <v>7</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="54">
-        <v>2.0950000000000002</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>101</v>
+      <c r="B9" s="64">
+        <v>1</v>
+      </c>
+      <c r="C9" s="64">
+        <v>1.036</v>
+      </c>
+      <c r="D9" s="64">
+        <v>7</v>
       </c>
       <c r="E9" s="60">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="56">
+      <c r="A10" s="57">
         <v>8</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="54">
-        <v>2.0960000000000001</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>101</v>
+      <c r="B10" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="64">
+        <v>1.054</v>
+      </c>
+      <c r="D10" s="64">
+        <v>7</v>
       </c>
       <c r="E10" s="60">
-        <v>0</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="56">
+      <c r="A11" s="57">
         <v>9</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="54">
-        <v>2.1</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>101</v>
+      <c r="B11" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="64">
+        <v>1.048</v>
+      </c>
+      <c r="D11" s="64">
+        <v>8.1</v>
       </c>
       <c r="E11" s="60">
-        <v>0</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="56">
+      <c r="A12" s="57">
         <v>10</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="54">
-        <v>2.101</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>101</v>
+      <c r="B12" s="64">
+        <v>1</v>
+      </c>
+      <c r="C12" s="64">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D12" s="64">
+        <v>8.1999999999999993</v>
       </c>
       <c r="E12" s="60">
-        <v>0</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="56">
+      <c r="A13" s="57">
         <v>11</v>
       </c>
-      <c r="B13" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="54">
-        <v>2.1040000000000001</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>101</v>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="64">
+        <v>1.038</v>
+      </c>
+      <c r="D13" s="64">
+        <v>8.1999999999999993</v>
       </c>
       <c r="E13" s="60">
-        <v>0</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="56">
+      <c r="A14" s="57">
         <v>12</v>
       </c>
-      <c r="B14" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="54">
-        <v>2.105</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>101</v>
+      <c r="B14" s="64">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1.026</v>
+      </c>
+      <c r="D14" s="64">
+        <v>9</v>
       </c>
       <c r="E14" s="60">
-        <v>0</v>
+        <v>191.68</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="56">
+      <c r="A15" s="57">
         <v>13</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>100</v>
+      <c r="B15" s="64">
+        <v>1</v>
       </c>
       <c r="C15" s="54">
-        <v>2.1070000000000002</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>101</v>
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D15" s="64">
+        <v>9</v>
       </c>
       <c r="E15" s="60">
-        <v>0</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="56">
+      <c r="A16" s="57">
         <v>14</v>
       </c>
-      <c r="B16" s="34" t="s">
-        <v>100</v>
+      <c r="B16" s="64">
+        <v>1</v>
       </c>
       <c r="C16" s="54">
-        <v>2.1080000000000001</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>101</v>
+        <v>1.028</v>
+      </c>
+      <c r="D16" s="64">
+        <v>9</v>
       </c>
       <c r="E16" s="60">
-        <v>0</v>
+        <v>68.81</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="71">
-        <f>SUM(E3:E16)</f>
-        <v>0</v>
+      <c r="A17" s="57">
+        <v>15</v>
+      </c>
+      <c r="B17" s="64">
+        <v>1</v>
+      </c>
+      <c r="C17" s="54">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D17" s="64">
+        <v>9</v>
+      </c>
+      <c r="E17" s="60">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="57">
+        <v>16</v>
+      </c>
+      <c r="B18" s="64">
+        <v>1</v>
+      </c>
+      <c r="C18" s="54">
+        <v>1.03</v>
+      </c>
+      <c r="D18" s="64">
+        <v>9</v>
+      </c>
+      <c r="E18" s="60">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="57">
+        <v>17</v>
+      </c>
+      <c r="B19" s="64">
+        <v>1</v>
+      </c>
+      <c r="C19" s="54">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D19" s="64">
+        <v>9</v>
+      </c>
+      <c r="E19" s="60">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="57">
+        <v>18</v>
+      </c>
+      <c r="B20" s="64">
+        <v>1</v>
+      </c>
+      <c r="C20" s="54">
+        <v>1.032</v>
+      </c>
+      <c r="D20" s="64">
+        <v>9</v>
+      </c>
+      <c r="E20" s="60">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="57">
+        <v>19</v>
+      </c>
+      <c r="B21" s="64">
+        <v>1</v>
+      </c>
+      <c r="C21" s="54">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D21" s="64">
+        <v>9</v>
+      </c>
+      <c r="E21" s="60">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="57">
+        <v>20</v>
+      </c>
+      <c r="B22" s="64">
+        <v>1</v>
+      </c>
+      <c r="C22" s="54">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D22" s="64">
+        <v>9</v>
+      </c>
+      <c r="E22" s="60">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="57">
+        <v>21</v>
+      </c>
+      <c r="B23" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C23" s="54">
+        <v>1.04</v>
+      </c>
+      <c r="D23" s="64">
+        <v>9</v>
+      </c>
+      <c r="E23" s="60">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="57">
+        <v>22</v>
+      </c>
+      <c r="B24" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="54">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D24" s="64">
+        <v>9</v>
+      </c>
+      <c r="E24" s="60">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="57">
+        <v>23</v>
+      </c>
+      <c r="B25" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" s="54">
+        <v>1.044</v>
+      </c>
+      <c r="D25" s="64">
+        <v>9</v>
+      </c>
+      <c r="E25" s="60">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="57">
+        <v>24</v>
+      </c>
+      <c r="B26" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="54">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D26" s="64">
+        <v>9</v>
+      </c>
+      <c r="E26" s="60">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="57">
+        <v>25</v>
+      </c>
+      <c r="B27" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="54">
+        <v>1.05</v>
+      </c>
+      <c r="D27" s="64">
+        <v>9</v>
+      </c>
+      <c r="E27" s="60">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="57">
+        <v>26</v>
+      </c>
+      <c r="B28" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="54">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D28" s="64">
+        <v>9</v>
+      </c>
+      <c r="E28" s="60">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="56"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="60">
+        <f>SUM(E3:E28)</f>
+        <v>2263.66</v>
       </c>
     </row>
   </sheetData>
@@ -4001,6 +4243,298 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="181" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="56">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="64">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="56">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="64">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="56">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="64">
+        <v>2.016</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="56">
+        <v>4</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="54">
+        <v>2.089</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="56">
+        <v>5</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="54">
+        <v>2.09</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="56">
+        <v>6</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="54">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="56">
+        <v>7</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="54">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="56">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="54">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="56">
+        <v>9</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="54">
+        <v>2.1</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="56">
+        <v>10</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="54">
+        <v>2.101</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="56">
+        <v>11</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="54">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="56">
+        <v>12</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="54">
+        <v>2.105</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="56">
+        <v>13</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="54">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="56">
+        <v>14</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="54">
+        <v>2.1080000000000001</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="56"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="71">
+        <f>SUM(E3:E16)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -4091,7 +4625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -4105,13 +4639,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -4609,7 +5143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -4624,13 +5158,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="85" t="s">
@@ -5009,7 +5543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -5022,13 +5556,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="181" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="181"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -5152,7 +5686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -5165,13 +5699,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="181" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="181"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
@@ -7298,7 +7832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -7853,7 +8387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -7865,13 +8399,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -7935,13 +8469,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="184" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="184"/>
+      <c r="B7" s="185"/>
+      <c r="C7" s="185"/>
+      <c r="D7" s="185"/>
+      <c r="E7" s="186"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -8004,13 +8538,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="182" t="s">
+      <c r="A13" s="184" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="183"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="184"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="186"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="85" t="s">
@@ -8493,7 +9027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -8505,13 +9039,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="187" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="s">
@@ -8577,13 +9111,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="185" t="s">
+      <c r="A7" s="187" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="185"/>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="85" t="s">
@@ -8666,13 +9200,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="185" t="s">
+      <c r="A14" s="187" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="185"/>
+      <c r="B14" s="187"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="187"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="85">
@@ -8708,151 +9242,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="0" tint="-0.14999847407452621"/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="185" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="85" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="85" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="85" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="85">
-        <v>4</v>
-      </c>
-      <c r="B3" s="85">
-        <v>1</v>
-      </c>
-      <c r="C3" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="85">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E3" s="100">
-        <v>14.79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="85">
-        <f>SUM(E3:E3)</f>
-        <v>14.79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="185" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="185"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="85" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="85" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="85">
-        <v>1</v>
-      </c>
-      <c r="B8" s="85">
-        <v>1</v>
-      </c>
-      <c r="C8" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="85">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E8" s="85">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="85">
-        <v>2</v>
-      </c>
-      <c r="B9" s="85">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="85">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E9" s="85">
-        <v>5.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="85">
-        <f>SUM(E8:E9)</f>
-        <v>11.98</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9194,6 +9583,151 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="187" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="85">
+        <v>4</v>
+      </c>
+      <c r="B3" s="85">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="85">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E3" s="100">
+        <v>14.79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="85">
+        <f>SUM(E3:E3)</f>
+        <v>14.79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="187" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="187"/>
+      <c r="C6" s="187"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="187"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="85">
+        <v>1</v>
+      </c>
+      <c r="B8" s="85">
+        <v>1</v>
+      </c>
+      <c r="C8" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="85">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E8" s="85">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="85">
+        <v>2</v>
+      </c>
+      <c r="B9" s="85">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="85">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9" s="85">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="85"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="85">
+        <f>SUM(E8:E9)</f>
+        <v>11.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -12318,7 +12852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -12333,18 +12867,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="190" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188" t="s">
+      <c r="B1" s="190"/>
+      <c r="C1" s="190" t="s">
         <v>339</v>
       </c>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188" t="s">
+      <c r="D1" s="190"/>
+      <c r="E1" s="190" t="s">
         <v>340</v>
       </c>
-      <c r="F1" s="188"/>
+      <c r="F1" s="190"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12571,22 +13105,22 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="187"/>
-      <c r="C15" s="187"/>
-      <c r="D15" s="187"/>
-      <c r="E15" s="187"/>
-      <c r="F15" s="187"/>
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="189"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="186" t="s">
+      <c r="A16" s="188" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
+      <c r="B16" s="188"/>
+      <c r="C16" s="188"/>
+      <c r="D16" s="188"/>
       <c r="E16" s="157" t="s">
         <v>2</v>
       </c>
@@ -12595,12 +13129,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="186" t="s">
+      <c r="A17" s="188" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="186"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="186"/>
+      <c r="B17" s="188"/>
+      <c r="C17" s="188"/>
+      <c r="D17" s="188"/>
       <c r="E17" s="157" t="s">
         <v>7</v>
       </c>
@@ -12622,7 +13156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -12637,14 +13171,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="190" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="160" t="s">
@@ -12762,21 +13296,21 @@
       <c r="F11" s="170"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="187" t="s">
+      <c r="A13" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B13" s="187"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
+      <c r="B13" s="189"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+      <c r="F13" s="189"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="190"/>
-      <c r="C14" s="191"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="193"/>
       <c r="D14" s="167" t="s">
         <v>341</v>
       </c>
@@ -12788,11 +13322,11 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="89.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="190"/>
-      <c r="C15" s="191"/>
+      <c r="B15" s="192"/>
+      <c r="C15" s="193"/>
       <c r="D15" s="167" t="s">
         <v>342</v>
       </c>
@@ -12817,7 +13351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -12835,21 +13369,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="191"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -12861,11 +13395,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="195" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="194"/>
-      <c r="C3" s="195"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="197"/>
       <c r="D3" s="167" t="s">
         <v>343</v>
       </c>
@@ -12884,10 +13418,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="196"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -12896,10 +13430,10 @@
       <c r="B5" s="162">
         <v>37.200000000000003</v>
       </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -12908,10 +13442,10 @@
       <c r="B6" s="162">
         <v>56.31</v>
       </c>
-      <c r="C6" s="198"/>
-      <c r="D6" s="199"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="199"/>
+      <c r="C6" s="200"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -12920,10 +13454,10 @@
       <c r="B7" s="162">
         <v>10.119999999999999</v>
       </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="199"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="199"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -12932,10 +13466,10 @@
       <c r="B8" s="162">
         <v>11.97</v>
       </c>
-      <c r="C8" s="198"/>
-      <c r="D8" s="199"/>
-      <c r="E8" s="199"/>
-      <c r="F8" s="199"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -12945,10 +13479,10 @@
         <f>SUM(B5:B8)</f>
         <v>115.60000000000001</v>
       </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="199"/>
-      <c r="F9" s="199"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="201"/>
+      <c r="F9" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12961,7 +13495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -12979,21 +13513,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="191"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13005,11 +13539,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="195" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="194"/>
-      <c r="C3" s="195"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="197"/>
       <c r="D3" s="167" t="s">
         <v>358</v>
       </c>
@@ -13028,10 +13562,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="196"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -13041,10 +13575,10 @@
         <f>379.31+(84.163-4)*0.1</f>
         <v>387.3263</v>
       </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -13054,10 +13588,10 @@
         <f>381.65+(83.53-2.2-1.8)*0.1</f>
         <v>389.60299999999995</v>
       </c>
-      <c r="C6" s="198"/>
-      <c r="D6" s="199"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="199"/>
+      <c r="C6" s="200"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -13067,10 +13601,10 @@
         <f>563.46+(102.28-1.5-2.2)*0.1</f>
         <v>573.31799999999998</v>
       </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="199"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="199"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -13080,10 +13614,10 @@
         <f>563.73+10</f>
         <v>573.73</v>
       </c>
-      <c r="C8" s="198"/>
-      <c r="D8" s="199"/>
-      <c r="E8" s="199"/>
-      <c r="F8" s="199"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -13093,10 +13627,10 @@
         <f>SUM(B5:B8)</f>
         <v>1923.9773</v>
       </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="199"/>
-      <c r="F9" s="199"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="201"/>
+      <c r="F9" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13109,7 +13643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -13127,21 +13661,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="191"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13153,11 +13687,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="195" t="s">
         <v>352</v>
       </c>
-      <c r="B3" s="194"/>
-      <c r="C3" s="195"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="197"/>
       <c r="D3" s="167" t="s">
         <v>354</v>
       </c>
@@ -13170,11 +13704,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="195" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="194"/>
-      <c r="C4" s="195"/>
+      <c r="B4" s="196"/>
+      <c r="C4" s="197"/>
       <c r="D4" s="167" t="s">
         <v>355</v>
       </c>
@@ -13187,16 +13721,16 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="189" t="s">
+      <c r="A5" s="191" t="s">
         <v>343</v>
       </c>
-      <c r="B5" s="191"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="189" t="s">
+      <c r="B5" s="193"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="191" t="s">
         <v>353</v>
       </c>
-      <c r="F5" s="191"/>
+      <c r="F5" s="193"/>
     </row>
     <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="160" t="s">
@@ -13205,8 +13739,8 @@
       <c r="B6" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="202"/>
-      <c r="D6" s="203"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="205"/>
       <c r="E6" s="160" t="s">
         <v>318</v>
       </c>
@@ -13221,8 +13755,8 @@
       <c r="B7" s="162">
         <v>379.31</v>
       </c>
-      <c r="C7" s="202"/>
-      <c r="D7" s="203"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="205"/>
       <c r="E7" s="161" t="s">
         <v>348</v>
       </c>
@@ -13237,8 +13771,8 @@
       <c r="B8" s="162">
         <v>381.65</v>
       </c>
-      <c r="C8" s="202"/>
-      <c r="D8" s="203"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="205"/>
       <c r="E8" s="161" t="s">
         <v>349</v>
       </c>
@@ -13253,8 +13787,8 @@
       <c r="B9" s="162">
         <v>563.46</v>
       </c>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203"/>
+      <c r="C9" s="204"/>
+      <c r="D9" s="205"/>
       <c r="E9" s="161" t="s">
         <v>350</v>
       </c>
@@ -13269,8 +13803,8 @@
       <c r="B10" s="162">
         <v>563.73</v>
       </c>
-      <c r="C10" s="202"/>
-      <c r="D10" s="203"/>
+      <c r="C10" s="204"/>
+      <c r="D10" s="205"/>
       <c r="E10" s="161" t="s">
         <v>351</v>
       </c>
@@ -13286,8 +13820,8 @@
         <f>SUM(B7:B10)</f>
         <v>1888.15</v>
       </c>
-      <c r="C11" s="202"/>
-      <c r="D11" s="203"/>
+      <c r="C11" s="204"/>
+      <c r="D11" s="205"/>
       <c r="E11" s="163" t="s">
         <v>337</v>
       </c>
@@ -13310,7 +13844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -13328,21 +13862,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="191"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193"/>
       <c r="D2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13354,11 +13888,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="67.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="195" t="s">
         <v>356</v>
       </c>
-      <c r="B3" s="194"/>
-      <c r="C3" s="195"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="197"/>
       <c r="D3" s="167" t="s">
         <v>343</v>
       </c>
@@ -13377,10 +13911,10 @@
       <c r="B4" s="160" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="196"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="161" t="s">
@@ -13389,10 +13923,10 @@
       <c r="B5" s="162">
         <v>379.31</v>
       </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="161" t="s">
@@ -13401,10 +13935,10 @@
       <c r="B6" s="162">
         <v>381.65</v>
       </c>
-      <c r="C6" s="198"/>
-      <c r="D6" s="199"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="199"/>
+      <c r="C6" s="200"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="161" t="s">
@@ -13413,10 +13947,10 @@
       <c r="B7" s="162">
         <v>563.46</v>
       </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="199"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="199"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="161" t="s">
@@ -13425,10 +13959,10 @@
       <c r="B8" s="162">
         <v>563.73</v>
       </c>
-      <c r="C8" s="198"/>
-      <c r="D8" s="199"/>
-      <c r="E8" s="199"/>
-      <c r="F8" s="199"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
@@ -13438,10 +13972,10 @@
         <f>SUM(B5:B8)</f>
         <v>1888.15</v>
       </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="199"/>
-      <c r="F9" s="199"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="201"/>
+      <c r="F9" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13449,73 +13983,6 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="C4:F9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="7" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="156"/>
-    <col min="2" max="2" width="49.6640625" style="156" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="156" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="156" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="156" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="156"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
-        <v>317</v>
-      </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-    </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="174" t="s">
-        <v>359</v>
-      </c>
-      <c r="B2" s="174" t="s">
-        <v>302</v>
-      </c>
-      <c r="C2" s="167" t="s">
-        <v>341</v>
-      </c>
-      <c r="D2" s="174" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="158" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="174">
-        <v>1</v>
-      </c>
-      <c r="B3" s="176" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="167" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="174" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="159">
-        <v>46.52</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13538,25 +14005,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="174" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="174" t="s">
         <v>302</v>
       </c>
       <c r="C2" s="167" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="177" t="s">
+      <c r="D2" s="174" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="158" t="s">
@@ -13564,20 +14031,20 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="177">
+      <c r="A3" s="174">
         <v>1</v>
       </c>
       <c r="B3" s="176" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="167" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="177" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="174" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="159">
-        <v>72.59</v>
+        <v>46.52</v>
       </c>
     </row>
   </sheetData>
@@ -13589,6 +14056,964 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="156"/>
+    <col min="2" max="2" width="49.6640625" style="156" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="156" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="156" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="156" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="189" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="177" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="177" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="177" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="177">
+        <v>1</v>
+      </c>
+      <c r="B3" s="176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="177" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="159">
+        <v>72.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7" style="11" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="11" customWidth="1"/>
+    <col min="3" max="6" width="8.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="37" customWidth="1"/>
+    <col min="8" max="10" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="180" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
+      <c r="B2" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="48">
+        <v>6.1</v>
+      </c>
+      <c r="D2" s="42">
+        <v>7.2</v>
+      </c>
+      <c r="E2" s="39">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F2" s="45">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="38">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I2" s="38">
+        <v>11</v>
+      </c>
+      <c r="J2" s="38">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="47">
+        <v>73.56</v>
+      </c>
+      <c r="G4" s="25">
+        <f>SUM(C4:F4)</f>
+        <v>73.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>2</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="47">
+        <v>72.239999999999995</v>
+      </c>
+      <c r="G5" s="25">
+        <f t="shared" ref="G5:G45" si="0">SUM(C5:F5)</f>
+        <v>72.239999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>3</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="47">
+        <v>68.260000000000005</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" si="0"/>
+        <v>68.260000000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>4</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="47">
+        <v>158.97</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="0"/>
+        <v>158.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>5</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="50">
+        <v>13.62</v>
+      </c>
+      <c r="D8" s="44"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="25">
+        <f t="shared" si="0"/>
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>6</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="47">
+        <v>68.3</v>
+      </c>
+      <c r="G9" s="25">
+        <f t="shared" si="0"/>
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="47">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G10" s="25">
+        <f t="shared" si="0"/>
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>8</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="47">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G11" s="25">
+        <f t="shared" si="0"/>
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
+        <v>9</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="47">
+        <v>67.53</v>
+      </c>
+      <c r="G12" s="25">
+        <f t="shared" si="0"/>
+        <v>67.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>10</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="47">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G13" s="25">
+        <f t="shared" si="0"/>
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>11</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="47">
+        <v>149.94999999999999</v>
+      </c>
+      <c r="G14" s="25">
+        <f t="shared" si="0"/>
+        <v>149.94999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>12</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="47">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G15" s="25">
+        <f t="shared" si="0"/>
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>13</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="44">
+        <v>17.22</v>
+      </c>
+      <c r="E16" s="41"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="25">
+        <f t="shared" si="0"/>
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>14</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="44">
+        <v>21.87</v>
+      </c>
+      <c r="E17" s="41"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="25">
+        <f t="shared" si="0"/>
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>15</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="50"/>
+      <c r="D18" s="44">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="E18" s="41"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="25">
+        <f t="shared" si="0"/>
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>16</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="41">
+        <v>3.22</v>
+      </c>
+      <c r="F19" s="47"/>
+      <c r="G19" s="25">
+        <f t="shared" si="0"/>
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>17</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="50"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="41">
+        <v>5.25</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="25">
+        <f t="shared" si="0"/>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>18</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="47">
+        <v>79.790000000000006</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>79.790000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>19</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="50"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="47">
+        <v>170.56</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="0"/>
+        <v>170.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>20</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="C23" s="50">
+        <v>16</v>
+      </c>
+      <c r="D23" s="44"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="25">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2.0870000000000002</v>
+      </c>
+      <c r="C24" s="50">
+        <v>19.46</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="25">
+        <f t="shared" si="0"/>
+        <v>19.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>22</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="47">
+        <v>10.24</v>
+      </c>
+      <c r="G25" s="25">
+        <f t="shared" si="0"/>
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="10">
+        <v>23</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="44">
+        <v>6.05</v>
+      </c>
+      <c r="E26" s="41"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="25">
+        <f t="shared" si="0"/>
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="10">
+        <v>24</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="44">
+        <v>12.15</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="25">
+        <f t="shared" si="0"/>
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <v>25</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="44">
+        <v>10.63</v>
+      </c>
+      <c r="E28" s="41"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="25">
+        <f t="shared" si="0"/>
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="10">
+        <v>26</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="50"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="47">
+        <v>23.36</v>
+      </c>
+      <c r="G29" s="25">
+        <f t="shared" si="0"/>
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="10">
+        <v>27</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="44">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="E30" s="41"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="25">
+        <f t="shared" si="0"/>
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="10">
+        <v>28</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="44">
+        <v>14.39</v>
+      </c>
+      <c r="E31" s="41"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="25">
+        <f t="shared" si="0"/>
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="10">
+        <v>29</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="50"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="41">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="F32" s="47"/>
+      <c r="G32" s="25">
+        <f t="shared" si="0"/>
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="10">
+        <v>30</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="41">
+        <v>4.76</v>
+      </c>
+      <c r="F33" s="47"/>
+      <c r="G33" s="25">
+        <f t="shared" si="0"/>
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
+        <v>31</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="50"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="47">
+        <v>21.09</v>
+      </c>
+      <c r="G34" s="25">
+        <f t="shared" si="0"/>
+        <v>21.09</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="10">
+        <v>32</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="50"/>
+      <c r="D35" s="44">
+        <v>8.19</v>
+      </c>
+      <c r="E35" s="41"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="25">
+        <f t="shared" si="0"/>
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="10">
+        <v>33</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="50"/>
+      <c r="D36" s="44">
+        <v>12.22</v>
+      </c>
+      <c r="E36" s="41"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="25">
+        <f t="shared" si="0"/>
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="10">
+        <v>34</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="50"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="41">
+        <v>9.24</v>
+      </c>
+      <c r="F37" s="47"/>
+      <c r="G37" s="25">
+        <f t="shared" si="0"/>
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="10">
+        <v>35</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="50"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="47">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="G38" s="25">
+        <f t="shared" si="0"/>
+        <v>19.329999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="10">
+        <v>36</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="50"/>
+      <c r="D39" s="44">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="E39" s="41"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="25">
+        <f t="shared" si="0"/>
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="10">
+        <v>37</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="50"/>
+      <c r="D40" s="44">
+        <v>14.25</v>
+      </c>
+      <c r="E40" s="41"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="25">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="10">
+        <v>38</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="47">
+        <v>19.36</v>
+      </c>
+      <c r="G41" s="25">
+        <f t="shared" si="0"/>
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="10">
+        <v>39</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="50"/>
+      <c r="D42" s="44">
+        <v>8.14</v>
+      </c>
+      <c r="E42" s="41"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="25">
+        <f>SUM(C42:F42)</f>
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
+        <v>40</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="50"/>
+      <c r="D43" s="44">
+        <v>16.28</v>
+      </c>
+      <c r="E43" s="41"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="25">
+        <f t="shared" si="0"/>
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="10">
+        <v>41</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="50">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="D44" s="44"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="25">
+        <f t="shared" si="0"/>
+        <v>33.049999999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
+        <v>42</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="50">
+        <v>8.02</v>
+      </c>
+      <c r="D45" s="44"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="25">
+        <f t="shared" si="0"/>
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="50">
+        <f>SUM(C4:C45)</f>
+        <v>90.149999999999991</v>
+      </c>
+      <c r="D46" s="44">
+        <f t="shared" ref="D46:F46" si="1">SUM(D4:D45)</f>
+        <v>163.69000000000003</v>
+      </c>
+      <c r="E46" s="41">
+        <f t="shared" si="1"/>
+        <v>27.32</v>
+      </c>
+      <c r="F46" s="47">
+        <f t="shared" si="1"/>
+        <v>1276.3799999999997</v>
+      </c>
+      <c r="G46" s="25">
+        <f>SUM(G4:G45)</f>
+        <v>1557.54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="13">
+        <v>2.16</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="11">
+        <v>2.081</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="11">
+        <v>2.085</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -13607,27 +15032,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="175" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="189" t="s">
+      <c r="B2" s="191" t="s">
         <v>302</v>
       </c>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="191"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="193"/>
       <c r="F2" s="167" t="s">
         <v>341</v>
       </c>
@@ -13642,12 +15067,12 @@
       <c r="A3" s="175">
         <v>1</v>
       </c>
-      <c r="B3" s="193" t="s">
+      <c r="B3" s="195" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="195"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="197"/>
       <c r="F3" s="167" t="s">
         <v>360</v>
       </c>
@@ -13660,14 +15085,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="204"/>
-      <c r="B4" s="204"/>
-      <c r="C4" s="204"/>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
+      <c r="A4" s="206"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="163" t="s">
@@ -13682,10 +15107,10 @@
       <c r="D5" s="163" t="s">
         <v>364</v>
       </c>
-      <c r="E5" s="205"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="206"/>
-      <c r="H5" s="206"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="163">
@@ -13700,10 +15125,10 @@
       <c r="D6" s="163">
         <v>6.03</v>
       </c>
-      <c r="E6" s="205"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="206"/>
-      <c r="H6" s="206"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="163" t="s">
@@ -13718,10 +15143,10 @@
       <c r="D7" s="163">
         <v>5.92</v>
       </c>
-      <c r="E7" s="205"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
+      <c r="E7" s="207"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C8" s="163" t="s">
@@ -13731,10 +15156,10 @@
         <f>SUM(B6:D7)</f>
         <v>47.740000000000009</v>
       </c>
-      <c r="E8" s="205"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="206"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13743,897 +15168,6 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="E5:H8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7" style="11" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="11" customWidth="1"/>
-    <col min="3" max="6" width="8.6640625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="37" customWidth="1"/>
-    <col min="8" max="10" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="48">
-        <v>6.1</v>
-      </c>
-      <c r="D2" s="42">
-        <v>7.2</v>
-      </c>
-      <c r="E2" s="39">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="F2" s="45">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="38">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I2" s="38">
-        <v>11</v>
-      </c>
-      <c r="J2" s="38">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
-        <v>1</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="47">
-        <v>73.56</v>
-      </c>
-      <c r="G4" s="25">
-        <f>SUM(C4:F4)</f>
-        <v>73.56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
-        <v>2</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="47">
-        <v>72.239999999999995</v>
-      </c>
-      <c r="G5" s="25">
-        <f t="shared" ref="G5:G45" si="0">SUM(C5:F5)</f>
-        <v>72.239999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
-        <v>3</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="47">
-        <v>68.260000000000005</v>
-      </c>
-      <c r="G6" s="25">
-        <f t="shared" si="0"/>
-        <v>68.260000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>4</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="47">
-        <v>158.97</v>
-      </c>
-      <c r="G7" s="25">
-        <f t="shared" si="0"/>
-        <v>158.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
-        <v>5</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="50">
-        <v>13.62</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="25">
-        <f t="shared" si="0"/>
-        <v>13.62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>6</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="47">
-        <v>68.3</v>
-      </c>
-      <c r="G9" s="25">
-        <f t="shared" si="0"/>
-        <v>68.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
-        <v>7</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="47">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="G10" s="25">
-        <f t="shared" si="0"/>
-        <v>68.459999999999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
-        <v>8</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="47">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="G11" s="25">
-        <f t="shared" si="0"/>
-        <v>68.459999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
-        <v>9</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="47">
-        <v>67.53</v>
-      </c>
-      <c r="G12" s="25">
-        <f t="shared" si="0"/>
-        <v>67.53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
-        <v>10</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="47">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="G13" s="25">
-        <f t="shared" si="0"/>
-        <v>68.459999999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
-        <v>11</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="47">
-        <v>149.94999999999999</v>
-      </c>
-      <c r="G14" s="25">
-        <f t="shared" si="0"/>
-        <v>149.94999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
-        <v>12</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="47">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="G15" s="25">
-        <f t="shared" si="0"/>
-        <v>68.459999999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
-        <v>13</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="44">
-        <v>17.22</v>
-      </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="25">
-        <f t="shared" si="0"/>
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
-        <v>14</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="44">
-        <v>21.87</v>
-      </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="25">
-        <f t="shared" si="0"/>
-        <v>21.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
-        <v>15</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="44">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="25">
-        <f t="shared" si="0"/>
-        <v>5.0599999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
-        <v>16</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="41">
-        <v>3.22</v>
-      </c>
-      <c r="F19" s="47"/>
-      <c r="G19" s="25">
-        <f t="shared" si="0"/>
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
-        <v>17</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="41">
-        <v>5.25</v>
-      </c>
-      <c r="F20" s="47"/>
-      <c r="G20" s="25">
-        <f t="shared" si="0"/>
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
-        <v>18</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="47">
-        <v>79.790000000000006</v>
-      </c>
-      <c r="G21" s="25">
-        <f t="shared" si="0"/>
-        <v>79.790000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
-        <v>19</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="47">
-        <v>170.56</v>
-      </c>
-      <c r="G22" s="25">
-        <f t="shared" si="0"/>
-        <v>170.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10">
-        <v>2.0840000000000001</v>
-      </c>
-      <c r="C23" s="50">
-        <v>16</v>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="25">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
-        <v>21</v>
-      </c>
-      <c r="B24" s="10">
-        <v>2.0870000000000002</v>
-      </c>
-      <c r="C24" s="50">
-        <v>19.46</v>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="25">
-        <f t="shared" si="0"/>
-        <v>19.46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
-        <v>22</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="47">
-        <v>10.24</v>
-      </c>
-      <c r="G25" s="25">
-        <f t="shared" si="0"/>
-        <v>10.24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
-        <v>23</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="44">
-        <v>6.05</v>
-      </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="25">
-        <f t="shared" si="0"/>
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
-        <v>24</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="44">
-        <v>12.15</v>
-      </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="25">
-        <f t="shared" si="0"/>
-        <v>12.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
-        <v>25</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="44">
-        <v>10.63</v>
-      </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="25">
-        <f t="shared" si="0"/>
-        <v>10.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
-        <v>26</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="47">
-        <v>23.36</v>
-      </c>
-      <c r="G29" s="25">
-        <f t="shared" si="0"/>
-        <v>23.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
-        <v>27</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="44">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="E30" s="41"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="25">
-        <f t="shared" si="0"/>
-        <v>8.7899999999999991</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
-        <v>28</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="44">
-        <v>14.39</v>
-      </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="25">
-        <f t="shared" si="0"/>
-        <v>14.39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
-        <v>29</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="41">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="F32" s="47"/>
-      <c r="G32" s="25">
-        <f t="shared" si="0"/>
-        <v>4.8499999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
-        <v>30</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="41">
-        <v>4.76</v>
-      </c>
-      <c r="F33" s="47"/>
-      <c r="G33" s="25">
-        <f t="shared" si="0"/>
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
-        <v>31</v>
-      </c>
-      <c r="B34" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="47">
-        <v>21.09</v>
-      </c>
-      <c r="G34" s="25">
-        <f t="shared" si="0"/>
-        <v>21.09</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
-        <v>32</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="44">
-        <v>8.19</v>
-      </c>
-      <c r="E35" s="41"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="25">
-        <f t="shared" si="0"/>
-        <v>8.19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="10">
-        <v>33</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="44">
-        <v>12.22</v>
-      </c>
-      <c r="E36" s="41"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="25">
-        <f t="shared" si="0"/>
-        <v>12.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
-        <v>34</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="41">
-        <v>9.24</v>
-      </c>
-      <c r="F37" s="47"/>
-      <c r="G37" s="25">
-        <f t="shared" si="0"/>
-        <v>9.24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
-        <v>35</v>
-      </c>
-      <c r="B38" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="50"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="47">
-        <v>19.329999999999998</v>
-      </c>
-      <c r="G38" s="25">
-        <f t="shared" si="0"/>
-        <v>19.329999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
-        <v>36</v>
-      </c>
-      <c r="B39" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="44">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="25">
-        <f t="shared" si="0"/>
-        <v>8.4499999999999993</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="10">
-        <v>37</v>
-      </c>
-      <c r="B40" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="50"/>
-      <c r="D40" s="44">
-        <v>14.25</v>
-      </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="25">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="10">
-        <v>38</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="47">
-        <v>19.36</v>
-      </c>
-      <c r="G41" s="25">
-        <f t="shared" si="0"/>
-        <v>19.36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
-        <v>39</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="50"/>
-      <c r="D42" s="44">
-        <v>8.14</v>
-      </c>
-      <c r="E42" s="41"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="25">
-        <f>SUM(C42:F42)</f>
-        <v>8.14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
-        <v>40</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="50"/>
-      <c r="D43" s="44">
-        <v>16.28</v>
-      </c>
-      <c r="E43" s="41"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="25">
-        <f t="shared" si="0"/>
-        <v>16.28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="10">
-        <v>41</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="50">
-        <v>33.049999999999997</v>
-      </c>
-      <c r="D44" s="44"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="25">
-        <f t="shared" si="0"/>
-        <v>33.049999999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
-        <v>42</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="50">
-        <v>8.02</v>
-      </c>
-      <c r="D45" s="44"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="25">
-        <f t="shared" si="0"/>
-        <v>8.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="50">
-        <f>SUM(C4:C45)</f>
-        <v>90.149999999999991</v>
-      </c>
-      <c r="D46" s="44">
-        <f t="shared" ref="D46:F46" si="1">SUM(D4:D45)</f>
-        <v>163.69000000000003</v>
-      </c>
-      <c r="E46" s="41">
-        <f t="shared" si="1"/>
-        <v>27.32</v>
-      </c>
-      <c r="F46" s="47">
-        <f t="shared" si="1"/>
-        <v>1276.3799999999997</v>
-      </c>
-      <c r="G46" s="25">
-        <f>SUM(G4:G45)</f>
-        <v>1557.54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="13">
-        <v>2.16</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="11">
-        <v>2.081</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="11">
-        <v>2.085</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -14968,6 +15502,198 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875" style="156" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="156" customWidth="1"/>
+    <col min="4" max="5" width="14.109375" style="156" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="156" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="156" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="156" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="156" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="156"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="189" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="178" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="179" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="167" t="s">
+        <v>341</v>
+      </c>
+      <c r="H2" s="178" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="158" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="73.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="178">
+        <v>1</v>
+      </c>
+      <c r="B3" s="179">
+        <v>202</v>
+      </c>
+      <c r="C3" s="195" t="s">
+        <v>367</v>
+      </c>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="167" t="s">
+        <v>372</v>
+      </c>
+      <c r="H3" s="178" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="159">
+        <f>D9</f>
+        <v>487.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="206"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="163" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" s="163" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="163" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="163" t="s">
+        <v>362</v>
+      </c>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="163" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="163">
+        <v>6</v>
+      </c>
+      <c r="D6" s="163">
+        <v>433.72</v>
+      </c>
+      <c r="E6" s="207"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
+      <c r="I6" s="208"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="163" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="163">
+        <v>7</v>
+      </c>
+      <c r="D7" s="163">
+        <v>7.73</v>
+      </c>
+      <c r="E7" s="207"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
+      <c r="I7" s="208"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="163" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" s="210" t="s">
+        <v>371</v>
+      </c>
+      <c r="D8" s="163">
+        <v>46.52</v>
+      </c>
+      <c r="E8" s="207"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="208"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C9" s="209" t="s">
+        <v>365</v>
+      </c>
+      <c r="D9" s="163">
+        <f>SUM(D6:D8)</f>
+        <v>487.97</v>
+      </c>
+      <c r="E9" s="207"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="208"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E5:I9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14979,15 +15705,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="180" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
@@ -15513,7 +16239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16624,7 +17350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -16975,7 +17701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -17064,504 +17790,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="9.109375" style="63"/>
-    <col min="5" max="5" width="9.109375" style="61"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="179" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="181"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="56">
-        <v>1</v>
-      </c>
-      <c r="B3" s="64">
-        <v>1</v>
-      </c>
-      <c r="C3" s="64">
-        <v>1.024</v>
-      </c>
-      <c r="D3" s="64">
-        <v>6</v>
-      </c>
-      <c r="E3" s="60">
-        <v>13.62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="57">
-        <v>2</v>
-      </c>
-      <c r="B4" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C4" s="64">
-        <v>1.0449999999999999</v>
-      </c>
-      <c r="D4" s="64">
-        <v>6</v>
-      </c>
-      <c r="E4" s="60">
-        <v>161.78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="57">
-        <v>3</v>
-      </c>
-      <c r="B5" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C5" s="64">
-        <v>1.046</v>
-      </c>
-      <c r="D5" s="64">
-        <v>6</v>
-      </c>
-      <c r="E5" s="60">
-        <v>161.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="57">
-        <v>4</v>
-      </c>
-      <c r="B6" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C6" s="64">
-        <v>1.0529999999999999</v>
-      </c>
-      <c r="D6" s="64">
-        <v>6</v>
-      </c>
-      <c r="E6" s="60">
-        <v>443.48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="57">
-        <v>5</v>
-      </c>
-      <c r="B7" s="64">
-        <v>1</v>
-      </c>
-      <c r="C7" s="64">
-        <v>1.034</v>
-      </c>
-      <c r="D7" s="64">
-        <v>7</v>
-      </c>
-      <c r="E7" s="60">
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="57">
-        <v>6</v>
-      </c>
-      <c r="B8" s="64">
-        <v>1</v>
-      </c>
-      <c r="C8" s="64">
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="D8" s="64">
-        <v>7</v>
-      </c>
-      <c r="E8" s="60">
-        <v>21.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="57">
-        <v>7</v>
-      </c>
-      <c r="B9" s="64">
-        <v>1</v>
-      </c>
-      <c r="C9" s="64">
-        <v>1.036</v>
-      </c>
-      <c r="D9" s="64">
-        <v>7</v>
-      </c>
-      <c r="E9" s="60">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="57">
-        <v>8</v>
-      </c>
-      <c r="B10" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C10" s="64">
-        <v>1.054</v>
-      </c>
-      <c r="D10" s="64">
-        <v>7</v>
-      </c>
-      <c r="E10" s="60">
-        <v>14.54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="57">
-        <v>9</v>
-      </c>
-      <c r="B11" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C11" s="64">
-        <v>1.048</v>
-      </c>
-      <c r="D11" s="64">
-        <v>8.1</v>
-      </c>
-      <c r="E11" s="60">
-        <v>23.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="57">
-        <v>10</v>
-      </c>
-      <c r="B12" s="64">
-        <v>1</v>
-      </c>
-      <c r="C12" s="64">
-        <v>1.0369999999999999</v>
-      </c>
-      <c r="D12" s="64">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E12" s="60">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="57">
-        <v>11</v>
-      </c>
-      <c r="B13" s="64">
-        <v>1</v>
-      </c>
-      <c r="C13" s="64">
-        <v>1.038</v>
-      </c>
-      <c r="D13" s="64">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E13" s="60">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="57">
-        <v>12</v>
-      </c>
-      <c r="B14" s="64">
-        <v>1</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1.026</v>
-      </c>
-      <c r="D14" s="64">
-        <v>9</v>
-      </c>
-      <c r="E14" s="60">
-        <v>191.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="57">
-        <v>13</v>
-      </c>
-      <c r="B15" s="64">
-        <v>1</v>
-      </c>
-      <c r="C15" s="54">
-        <v>1.0269999999999999</v>
-      </c>
-      <c r="D15" s="64">
-        <v>9</v>
-      </c>
-      <c r="E15" s="60">
-        <v>114.04</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="57">
-        <v>14</v>
-      </c>
-      <c r="B16" s="64">
-        <v>1</v>
-      </c>
-      <c r="C16" s="54">
-        <v>1.028</v>
-      </c>
-      <c r="D16" s="64">
-        <v>9</v>
-      </c>
-      <c r="E16" s="60">
-        <v>68.81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="57">
-        <v>15</v>
-      </c>
-      <c r="B17" s="64">
-        <v>1</v>
-      </c>
-      <c r="C17" s="54">
-        <v>1.0289999999999999</v>
-      </c>
-      <c r="D17" s="64">
-        <v>9</v>
-      </c>
-      <c r="E17" s="60">
-        <v>68.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="57">
-        <v>16</v>
-      </c>
-      <c r="B18" s="64">
-        <v>1</v>
-      </c>
-      <c r="C18" s="54">
-        <v>1.03</v>
-      </c>
-      <c r="D18" s="64">
-        <v>9</v>
-      </c>
-      <c r="E18" s="60">
-        <v>68.89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="57">
-        <v>17</v>
-      </c>
-      <c r="B19" s="64">
-        <v>1</v>
-      </c>
-      <c r="C19" s="54">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="D19" s="64">
-        <v>9</v>
-      </c>
-      <c r="E19" s="60">
-        <v>68.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="57">
-        <v>18</v>
-      </c>
-      <c r="B20" s="64">
-        <v>1</v>
-      </c>
-      <c r="C20" s="54">
-        <v>1.032</v>
-      </c>
-      <c r="D20" s="64">
-        <v>9</v>
-      </c>
-      <c r="E20" s="60">
-        <v>68.069999999999993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="57">
-        <v>19</v>
-      </c>
-      <c r="B21" s="64">
-        <v>1</v>
-      </c>
-      <c r="C21" s="54">
-        <v>1.0329999999999999</v>
-      </c>
-      <c r="D21" s="64">
-        <v>9</v>
-      </c>
-      <c r="E21" s="60">
-        <v>139.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="57">
-        <v>20</v>
-      </c>
-      <c r="B22" s="64">
-        <v>1</v>
-      </c>
-      <c r="C22" s="54">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="D22" s="64">
-        <v>9</v>
-      </c>
-      <c r="E22" s="60">
-        <v>149.69999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="57">
-        <v>21</v>
-      </c>
-      <c r="B23" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C23" s="54">
-        <v>1.04</v>
-      </c>
-      <c r="D23" s="64">
-        <v>9</v>
-      </c>
-      <c r="E23" s="60">
-        <v>220.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="57">
-        <v>22</v>
-      </c>
-      <c r="B24" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C24" s="54">
-        <v>1.0429999999999999</v>
-      </c>
-      <c r="D24" s="64">
-        <v>9</v>
-      </c>
-      <c r="E24" s="60">
-        <v>61.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="57">
-        <v>23</v>
-      </c>
-      <c r="B25" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C25" s="54">
-        <v>1.044</v>
-      </c>
-      <c r="D25" s="64">
-        <v>9</v>
-      </c>
-      <c r="E25" s="60">
-        <v>14.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="57">
-        <v>24</v>
-      </c>
-      <c r="B26" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C26" s="54">
-        <v>1.0489999999999999</v>
-      </c>
-      <c r="D26" s="64">
-        <v>9</v>
-      </c>
-      <c r="E26" s="60">
-        <v>103.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="57">
-        <v>25</v>
-      </c>
-      <c r="B27" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C27" s="54">
-        <v>1.05</v>
-      </c>
-      <c r="D27" s="64">
-        <v>9</v>
-      </c>
-      <c r="E27" s="60">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="57">
-        <v>26</v>
-      </c>
-      <c r="B28" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C28" s="54">
-        <v>1.0509999999999999</v>
-      </c>
-      <c r="D28" s="64">
-        <v>9</v>
-      </c>
-      <c r="E28" s="60">
-        <v>31.58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="60">
-        <f>SUM(E3:E28)</f>
-        <v>2263.66</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>